--- a/exports/trend_1d/JIOFIN_full_report.xlsx
+++ b/exports/trend_1d/JIOFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>15</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45216</v>
+        <v>45217</v>
       </c>
       <c r="H2" t="n">
-        <v>220.95</v>
+        <v>216</v>
       </c>
       <c r="I2" t="n">
         <v>219.077813195</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.82</v>
+        <v>-14.78</v>
       </c>
       <c r="L2" t="n">
-        <v>13.65</v>
+        <v>14.95</v>
       </c>
       <c r="M2" t="n">
         <v>3.16</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="H3" t="n">
-        <v>226.05</v>
+        <v>229.4</v>
       </c>
       <c r="I3" t="n">
         <v>228.1205018623129</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.65</v>
+        <v>-6.2</v>
       </c>
       <c r="L3" t="n">
         <v>7.55</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H4" t="n">
-        <v>246.45</v>
+        <v>240.4</v>
       </c>
       <c r="I4" t="n">
         <v>241.9655987664286</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>7.43</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>2.94</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>11.24</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H5" t="n">
-        <v>253.8</v>
+        <v>289.1</v>
       </c>
       <c r="I5" t="n">
         <v>261.7240647158733</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.57</v>
+        <v>-20.26</v>
       </c>
       <c r="L5" t="n">
-        <v>7.03</v>
+        <v>23</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>4.65</v>
+        <v>13.91</v>
       </c>
       <c r="O5" t="n">
         <v>-2.45</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.76</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H6" t="n">
-        <v>355.2</v>
+        <v>345.4</v>
       </c>
       <c r="I6" t="n">
         <v>349.6544769520224</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K6" t="n">
-        <v>22.86</v>
+        <v>19.47</v>
       </c>
       <c r="L6" t="n">
         <v>11.55</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45534</v>
+        <v>45537</v>
       </c>
       <c r="H7" t="n">
-        <v>321.7</v>
+        <v>344.9</v>
       </c>
       <c r="I7" t="n">
         <v>338.7011816986106</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K7" t="n">
-        <v>6.86</v>
+        <v>0.14</v>
       </c>
       <c r="L7" t="n">
         <v>8.859999999999999</v>
@@ -840,7 +923,7 @@
         <v>6.87</v>
       </c>
       <c r="N7" t="n">
-        <v>5.91</v>
+        <v>7.21</v>
       </c>
       <c r="O7" t="n">
         <v>-2.76</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.78</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H8" t="n">
-        <v>330.35</v>
+        <v>327.2</v>
       </c>
       <c r="I8" t="n">
         <v>327.2560667193499</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.22</v>
+        <v>-5.13</v>
       </c>
       <c r="L8" t="n">
         <v>6.31</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.41</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H9" t="n">
-        <v>326.05</v>
+        <v>328.9</v>
       </c>
       <c r="I9" t="n">
         <v>327.7058889614198</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>-0.52</v>
       </c>
       <c r="L9" t="n">
         <v>2.2</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>8.34</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H10" t="n">
-        <v>324.6</v>
+        <v>313</v>
       </c>
       <c r="I10" t="n">
         <v>319.1931900227105</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.31</v>
+        <v>-4.83</v>
       </c>
       <c r="L10" t="n">
-        <v>1.98</v>
+        <v>5.52</v>
       </c>
       <c r="M10" t="n">
-        <v>0.72</v>
+        <v>2.03</v>
       </c>
       <c r="N10" t="n">
         <v>3.71</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H11" t="n">
-        <v>228.84</v>
+        <v>231.69</v>
       </c>
       <c r="I11" t="n">
         <v>230.5572075032649</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="n">
-        <v>26.89</v>
+        <v>25.98</v>
       </c>
       <c r="L11" t="n">
         <v>2.2</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H12" t="n">
-        <v>311.25</v>
+        <v>307.35</v>
       </c>
       <c r="I12" t="n">
         <v>310.6397919478887</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K12" t="n">
-        <v>34.34</v>
+        <v>32.66</v>
       </c>
       <c r="L12" t="n">
         <v>12.34</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.89</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="H13" t="n">
-        <v>329.5</v>
+        <v>333.9</v>
       </c>
       <c r="I13" t="n">
         <v>331.6009593778177</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.21</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>8.25</v>
+        <v>9.16</v>
       </c>
       <c r="M13" t="n">
         <v>0.59</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>7.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="H14" t="n">
-        <v>315.75</v>
+        <v>310.1</v>
       </c>
       <c r="I14" t="n">
         <v>311.3146173222932</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.44</v>
+        <v>-7.13</v>
       </c>
       <c r="L14" t="n">
-        <v>5.9</v>
+        <v>7.31</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="H15" t="n">
-        <v>305.6</v>
+        <v>312.65</v>
       </c>
       <c r="I15" t="n">
         <v>311.2749382486519</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>1.45</v>
+        <v>-0.82</v>
       </c>
       <c r="L15" t="n">
         <v>3.71</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.48</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H16" t="n">
-        <v>303.75</v>
+        <v>297.2</v>
       </c>
       <c r="I16" t="n">
         <v>297.2342455597714</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.85</v>
+        <v>-4.94</v>
       </c>
       <c r="L16" t="n">
         <v>6.13</v>
@@ -1353,7 +1544,7 @@
         <v>0.57</v>
       </c>
       <c r="N16" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
         <v>2.31</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H17" t="n">
-        <v>263.9</v>
+        <v>268</v>
       </c>
       <c r="I17" t="n">
         <v>266.9649384040189</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K17" t="n">
-        <v>11.2</v>
+        <v>9.83</v>
       </c>
       <c r="L17" t="n">
         <v>2.96</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>11.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H18" t="n">
-        <v>249</v>
+        <v>241.3</v>
       </c>
       <c r="I18" t="n">
         <v>248.3669320196298</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.09</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>9.119999999999999</v>
+        <v>10.52</v>
       </c>
       <c r="M18" t="n">
         <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
       <c r="O18" t="n">
         <v>1.55</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.18</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H19" t="n">
-        <v>245.73</v>
+        <v>253.64</v>
       </c>
       <c r="I19" t="n">
         <v>250.2944482196268</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.84</v>
+        <v>-5.11</v>
       </c>
       <c r="L19" t="n">
-        <v>4.93</v>
+        <v>5.55</v>
       </c>
       <c r="M19" t="n">
         <v>4.15</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.69</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H20" t="n">
-        <v>240.33</v>
+        <v>230.47</v>
       </c>
       <c r="I20" t="n">
         <v>231.3837573137996</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.25</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>5.46</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>1.34</v>
       </c>
       <c r="N20" t="n">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>3.22</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>11.31</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H21" t="n">
-        <v>237.08</v>
+        <v>249.48</v>
       </c>
       <c r="I21" t="n">
         <v>244.9544825869918</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.87</v>
+        <v>-8.25</v>
       </c>
       <c r="L21" t="n">
-        <v>8.449999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="M21" t="n">
         <v>5.03</v>
       </c>
       <c r="N21" t="n">
-        <v>3.68</v>
+        <v>5.23</v>
       </c>
       <c r="O21" t="n">
         <v>-4.1</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H22" t="n">
-        <v>245.8</v>
+        <v>243.15</v>
       </c>
       <c r="I22" t="n">
         <v>244.0728219921632</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.48</v>
+        <v>-2.54</v>
       </c>
       <c r="L22" t="n">
         <v>4.8</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1755,6 +2030,14 @@
       <c r="Q23" t="n">
         <v>48</v>
       </c>
+      <c r="R23" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3211,7 +3494,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="6">
@@ -3221,7 +3504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -3231,7 +3514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -3241,7 +3524,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3251,7 +3534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -3261,7 +3544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -3301,7 +3584,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.32</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="15">
@@ -3311,7 +3594,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="16">
@@ -3321,7 +3604,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.46</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="17">
@@ -3331,7 +3614,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.34</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="18">
@@ -3341,7 +3624,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.1</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="19">
@@ -3351,7 +3634,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.49</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="20">
@@ -3361,7 +3644,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.13</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="21">
@@ -3371,7 +3654,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -3381,7 +3664,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -3391,7 +3674,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -3401,7 +3684,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="25">
@@ -3421,7 +3704,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.31</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="27">
@@ -3431,7 +3714,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.300000000000001</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="28">
@@ -3441,7 +3724,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
